--- a/templates/upcoming_fixtures_template.xlsx
+++ b/templates/upcoming_fixtures_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>kickoff_time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>home_team</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>away_team</t>
         </is>
@@ -473,10 +478,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>Example Home</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Example Away</t>
         </is>
